--- a/data/hardtail/Esker Hayduke Ti 2025.xlsx
+++ b/data/hardtail/Esker Hayduke Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9BC047-2652-6F49-923B-095658CA097E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51A8A1A-76EA-114F-8491-EB61EFA638D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="500" windowWidth="26100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -263,18 +263,6 @@
     <t>Esker</t>
   </si>
   <si>
-    <t>S1/SM </t>
-  </si>
-  <si>
-    <t>S2/MD </t>
-  </si>
-  <si>
-    <t>S3/LG </t>
-  </si>
-  <si>
-    <t>S4/XL </t>
-  </si>
-  <si>
     <t>Effective TT Length</t>
   </si>
   <si>
@@ -363,6 +351,21 @@
   </si>
   <si>
     <t>Hayduke Ti</t>
+  </si>
+  <si>
+    <t>frame size</t>
+  </si>
+  <si>
+    <t>S1/SM</t>
+  </si>
+  <si>
+    <t>S2/MD</t>
+  </si>
+  <si>
+    <t>S3/LG</t>
+  </si>
+  <si>
+    <t>S4/XL</t>
   </si>
 </sst>
 </file>
@@ -758,7 +761,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -782,7 +785,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="23">
@@ -793,24 +796,27 @@
         <v>70</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>76</v>
+      <c r="B8" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>79</v>
+        <v>109</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -818,7 +824,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C9" s="3">
         <v>597</v>
@@ -838,7 +844,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C10" s="3">
         <v>420</v>
@@ -858,7 +864,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C11" s="3">
         <v>615</v>
@@ -878,7 +884,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3">
         <v>67.5</v>
@@ -898,7 +904,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C13" s="3">
         <v>105</v>
@@ -918,7 +924,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C14" s="3">
         <v>74</v>
@@ -938,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C15" s="3">
         <v>380</v>
@@ -955,10 +961,10 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C16" s="3">
         <v>280</v>
@@ -978,7 +984,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C17" s="3">
         <v>440</v>
@@ -993,16 +999,16 @@
         <v>440</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1010,7 +1016,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C18" s="3">
         <v>44</v>
@@ -1030,7 +1036,7 @@
         <v>20</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C19" s="3">
         <v>495</v>
@@ -1050,7 +1056,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C20" s="3">
         <v>65</v>
@@ -1070,7 +1076,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C21" s="3">
         <v>1130</v>
@@ -1090,7 +1096,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C22" s="3">
         <v>50</v>
@@ -1108,7 +1114,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B23" s="6"/>
       <c r="D23" s="3">
@@ -1291,19 +1297,19 @@
         <v>72</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1311,7 +1317,7 @@
         <v>73</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1319,7 +1325,7 @@
         <v>74</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1407,7 +1413,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1428,7 +1434,7 @@
         <v>49</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1558,7 +1564,7 @@
         <v>69</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
